--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEW_YORK_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEW_YORK_2012.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C117">
@@ -2965,7 +2965,7 @@
         <v>233</v>
       </c>
       <c r="D145">
-        <v>0.009319254459643</v>
+        <v>0.009319254459643002</v>
       </c>
     </row>
     <row r="146">
@@ -3379,7 +3379,7 @@
         <v>24</v>
       </c>
       <c r="D168">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="169">
@@ -9769,7 +9769,7 @@
         <v>24</v>
       </c>
       <c r="D523">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="524">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C555">
@@ -10705,7 +10705,7 @@
         <v>24</v>
       </c>
       <c r="D575">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="576">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C675">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C676">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C723">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C724">
@@ -16249,7 +16249,7 @@
         <v>24</v>
       </c>
       <c r="D883">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="884">
@@ -17401,7 +17401,7 @@
         <v>24</v>
       </c>
       <c r="D947">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="948">
@@ -18139,7 +18139,7 @@
         <v>24</v>
       </c>
       <c r="D988">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="989">
@@ -18697,7 +18697,7 @@
         <v>24</v>
       </c>
       <c r="D1019">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="1020">
@@ -20724,7 +20724,7 @@
       </c>
       <c r="B1132" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1132">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1177">
@@ -23629,7 +23629,7 @@
         <v>24</v>
       </c>
       <c r="D1293">
-        <v>0.000959923206144</v>
+        <v>0.0009599232061440002</v>
       </c>
     </row>
     <row r="1294">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1302">
